--- a/incident_report_forms/046_guest_service_incident_report_form--incident_report_forms.xlsx
+++ b/incident_report_forms/046_guest_service_incident_report_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -531,30 +531,30 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>guest_name</t>
+          <t>incident_category</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Guest Name</t>
+          <t>Incident Category</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>incident_category</t>
+          <t>incident_location</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Incident Category</t>
+          <t>Incident Location</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,68 +589,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>incident_details</t>
+          <t>incident_description</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Incident Details</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Please describe the incident in as much detail as possible.</t>
-        </is>
-      </c>
+          <t>Incident Description</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>guest_room</t>
+          <t>action_taken</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Guest Room</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>incident_location</t>
+          <t>guest_name</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Incident Location</t>
+          <t>Guest Name</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,436 +658,179 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>incident_description</t>
+          <t>guest_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Incident Description</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Please provide a detailed description of the incident.</t>
-        </is>
-      </c>
+          <t>Guest Email</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>action_taken</t>
+          <t>employee_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Action Taken</t>
+          <t>Employee Name</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>employee_name</t>
+          <t>employee_department</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Employee Name</t>
+          <t>Employee Department</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>employee_department</t>
+          <t>employee_id</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Employee Department</t>
+          <t>Employee ID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>employee_id</t>
+          <t>follow_up_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Employee ID</t>
+          <t>Follow-up Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>guest_email</t>
+          <t>follow_up_status</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Guest Email</t>
+          <t>Follow-up Status</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>follow_up_date</t>
+          <t>employee_confirmation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Follow-up Date</t>
+          <t>Employee Confirmation</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>follow_up_status</t>
+          <t>guest_confirmation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Follow-up Status</t>
+          <t>Guest Confirmation</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>action_taken</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>employee_department</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Employee Department</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>employee_id</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>guest_email</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Guest Email</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>follow_up_date</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Follow-up Date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>follow_up_status</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Follow-up Status</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>employee_name</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Employee Name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>employee_department</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Employee Department</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>employee_id</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>guest_email</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Guest Email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>follow_up_date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Follow-up Date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1106,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1219,51 +958,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>guest_room_choices</t>
+          <t>incident_location_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>room_1</t>
+          <t>front_desk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Room 1</t>
+          <t>Front Desk</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>guest_room_choices</t>
+          <t>incident_location_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>room_2</t>
+          <t>pool_area</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Room 2</t>
+          <t>Pool Area</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>guest_room_choices</t>
+          <t>incident_location_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>room_3</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Room 3</t>
+          <t>Restaurant</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>front_desk</t>
+          <t>room</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Front Desk</t>
+          <t>Room</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pool_area</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pool Area</t>
+          <t>Parking</t>
         </is>
       </c>
     </row>
@@ -1309,63 +1048,63 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Restaurant</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>incident_location_choices</t>
+          <t>action_taken_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>room</t>
+          <t>follow-up</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Room</t>
+          <t>Follow-up</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>incident_location_choices</t>
+          <t>action_taken_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Review</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>incident_location_choices</t>
+          <t>action_taken_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>resolution</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Resolution</t>
         </is>
       </c>
     </row>
@@ -1377,63 +1116,63 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>follow-up</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Follow-up</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>action_taken_choices</t>
+          <t>employee_department_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>front_desk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Front Desk</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>action_taken_choices</t>
+          <t>employee_department_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>resolution</t>
+          <t>food_and_beverage</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Food and Beverage</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>action_taken_choices</t>
+          <t>employee_department_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>housekeeping</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Housekeeping</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>front_desk</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Front Desk</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -1462,335 +1201,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>food_and_beverage</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Food and Beverage</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>employee_department_choices</t>
+          <t>follow_up_status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>housekeeping</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Housekeeping</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>employee_department_choices</t>
+          <t>follow_up_status_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>engineering</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>employee_department_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>employee_id_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>employee_id_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>In progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>employee_department_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>front_desk</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Front Desk</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>employee_department_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>food_and_beverage</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Food and Beverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>employee_department_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>housekeeping</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Housekeeping</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>employee_department_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>engineering</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>employee_department_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>employee_department_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>front_desk</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Front Desk</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>employee_department_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>food_and_beverage</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Food and Beverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>employee_department_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>housekeeping</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Housekeeping</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>employee_department_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>engineering</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>employee_department_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>
